--- a/artfynd/A 17415-2022 artfynd.xlsx
+++ b/artfynd/A 17415-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17415-2022 artfynd.xlsx
+++ b/artfynd/A 17415-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101620981</v>
+        <v>101620948</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599533.8658874059</v>
+        <v>599174</v>
       </c>
       <c r="R2" t="n">
-        <v>7014678.465794126</v>
+        <v>7014691</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101621009</v>
+        <v>101620951</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,12 +792,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599024.3528086075</v>
+        <v>599043</v>
       </c>
       <c r="R3" t="n">
-        <v>7014658.703457096</v>
+        <v>7014635</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -860,19 +840,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101621017</v>
+        <v>101620955</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599212.8672958526</v>
+        <v>599186</v>
       </c>
       <c r="R4" t="n">
-        <v>7014679.381740093</v>
+        <v>7014704</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -972,19 +937,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101620962</v>
+        <v>101620957</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599344.3562168549</v>
+        <v>599239</v>
       </c>
       <c r="R5" t="n">
-        <v>7014572.982262874</v>
+        <v>7014702</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1084,19 +1034,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101620946</v>
+        <v>101620959</v>
       </c>
       <c r="B6" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599022.5072355319</v>
+        <v>599343</v>
       </c>
       <c r="R6" t="n">
-        <v>7014659.999173108</v>
+        <v>7014570</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1196,19 +1131,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101620977</v>
+        <v>101620967</v>
       </c>
       <c r="B7" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>599270.5889054096</v>
+        <v>599331</v>
       </c>
       <c r="R7" t="n">
-        <v>7014696.037221982</v>
+        <v>7014558</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1308,19 +1228,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101620975</v>
+        <v>101620970</v>
       </c>
       <c r="B8" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>599193.8767205492</v>
+        <v>599375</v>
       </c>
       <c r="R8" t="n">
-        <v>7014695.026225518</v>
+        <v>7014559</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1420,19 +1325,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101620965</v>
+        <v>101620973</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>599525.7194602716</v>
+        <v>599390</v>
       </c>
       <c r="R9" t="n">
-        <v>7014606.081893392</v>
+        <v>7014584</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1532,19 +1422,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101621015</v>
+        <v>101620980</v>
       </c>
       <c r="B10" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,12 +1471,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>599365.4227363134</v>
+        <v>599391</v>
       </c>
       <c r="R10" t="n">
-        <v>7014563.262878499</v>
+        <v>7014682</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1644,19 +1519,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101620980</v>
+        <v>101620990</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,12 +1568,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>599391.0838521578</v>
+        <v>599545</v>
       </c>
       <c r="R11" t="n">
-        <v>7014682.622190851</v>
+        <v>7014664</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1756,19 +1616,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101620956</v>
+        <v>101620991</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>599282.578367833</v>
+        <v>599380</v>
       </c>
       <c r="R12" t="n">
-        <v>7014717.144247995</v>
+        <v>7014556</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1868,19 +1713,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101620987</v>
+        <v>101620996</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>599025.4071435396</v>
+        <v>599458</v>
       </c>
       <c r="R13" t="n">
-        <v>7014653.776860707</v>
+        <v>7014692</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1980,19 +1810,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101620993</v>
+        <v>101621002</v>
       </c>
       <c r="B14" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>599284.522027344</v>
+        <v>599420</v>
       </c>
       <c r="R14" t="n">
-        <v>7014654.089694151</v>
+        <v>7014707</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2092,19 +1907,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101620997</v>
+        <v>101621006</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>599522.9716134741</v>
+        <v>599235</v>
       </c>
       <c r="R15" t="n">
-        <v>7014607.34948095</v>
+        <v>7014707</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2204,19 +2004,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101620966</v>
+        <v>101621009</v>
       </c>
       <c r="B16" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>599298.5649891923</v>
+        <v>599024</v>
       </c>
       <c r="R16" t="n">
-        <v>7014696.448782376</v>
+        <v>7014659</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2316,19 +2101,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101620996</v>
+        <v>101621015</v>
       </c>
       <c r="B17" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,12 +2150,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>599457.5961841721</v>
+        <v>599365</v>
       </c>
       <c r="R17" t="n">
-        <v>7014692.339263345</v>
+        <v>7014563</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2428,19 +2198,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,15 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101620971</v>
+        <v>101621019</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,39 +2238,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>599395.470230437</v>
+        <v>599191</v>
       </c>
       <c r="R18" t="n">
-        <v>7014657.511581922</v>
+        <v>7014703</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2545,19 +2295,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,53 +2324,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101621001</v>
+        <v>103429199</v>
       </c>
       <c r="B19" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>599000.2140297719</v>
+        <v>599063</v>
       </c>
       <c r="R19" t="n">
-        <v>7014665.625328016</v>
+        <v>7014673</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,22 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2680,31 +2405,35 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101620954</v>
+        <v>103429200</v>
       </c>
       <c r="B20" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,37 +2441,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>599375.5119706019</v>
+        <v>599292</v>
       </c>
       <c r="R20" t="n">
-        <v>7014558.164106351</v>
+        <v>7014694</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,22 +2495,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,31 +2511,35 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101620992</v>
+        <v>103429201</v>
       </c>
       <c r="B21" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2824,37 +2547,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>599248.2053604436</v>
+        <v>599261</v>
       </c>
       <c r="R21" t="n">
-        <v>7014660.63440095</v>
+        <v>7014619</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,22 +2601,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2904,31 +2617,35 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101621019</v>
+        <v>103429205</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,28 +2662,28 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>599190.9210342165</v>
+        <v>599278</v>
       </c>
       <c r="R22" t="n">
-        <v>7014703.049867166</v>
+        <v>7014605</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,22 +2707,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,31 +2723,35 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101620953</v>
+        <v>103429207</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3048,37 +2759,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>599393.3479170343</v>
+        <v>599058</v>
       </c>
       <c r="R23" t="n">
-        <v>7014638.511484101</v>
+        <v>7014638</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,22 +2813,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,69 +2829,73 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101621007</v>
+        <v>103429209</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>599503.9521863075</v>
+        <v>599401</v>
       </c>
       <c r="R24" t="n">
-        <v>7014696.926760311</v>
+        <v>7014629</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,22 +2919,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,31 +2935,35 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101620974</v>
+        <v>103429210</v>
       </c>
       <c r="B25" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,42 +2971,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>599272.2968894818</v>
+        <v>599502</v>
       </c>
       <c r="R25" t="n">
-        <v>7014582.031393103</v>
+        <v>7014627</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3331,22 +3025,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,31 +3041,35 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>101620949</v>
+        <v>103429211</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3389,37 +3077,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>599233.5164604351</v>
+        <v>599244</v>
       </c>
       <c r="R26" t="n">
-        <v>7014712.4765905</v>
+        <v>7014606</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3443,22 +3131,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3469,31 +3147,35 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101620972</v>
+        <v>103429208</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3501,37 +3183,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>599211.7503722769</v>
+        <v>599491</v>
       </c>
       <c r="R27" t="n">
-        <v>7014700.986517719</v>
+        <v>7014607</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3555,22 +3237,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3581,53 +3253,57 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101621016</v>
+        <v>101620964</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3313,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>599196.8046786126</v>
+        <v>599494</v>
       </c>
       <c r="R28" t="n">
-        <v>7014687.903344741</v>
+        <v>7014657</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3670,19 +3346,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3709,15 +3375,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101620959</v>
+        <v>101620949</v>
       </c>
       <c r="B29" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3725,21 +3386,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3749,10 +3410,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>599343.5514165146</v>
+        <v>599234</v>
       </c>
       <c r="R29" t="n">
-        <v>7014569.801602065</v>
+        <v>7014713</v>
       </c>
       <c r="S29" t="n">
         <v>50</v>
@@ -3782,19 +3443,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,15 +3472,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101620951</v>
+        <v>101620952</v>
       </c>
       <c r="B30" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3837,21 +3483,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3861,10 +3507,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>599043.5920237565</v>
+        <v>599263</v>
       </c>
       <c r="R30" t="n">
-        <v>7014634.950694547</v>
+        <v>7014703</v>
       </c>
       <c r="S30" t="n">
         <v>50</v>
@@ -3894,19 +3540,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,15 +3569,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101621006</v>
+        <v>101620953</v>
       </c>
       <c r="B31" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3949,21 +3580,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3973,10 +3604,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>599234.571103176</v>
+        <v>599394</v>
       </c>
       <c r="R31" t="n">
-        <v>7014707.550132813</v>
+        <v>7014639</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4006,19 +3637,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,15 +3666,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101621018</v>
+        <v>101620954</v>
       </c>
       <c r="B32" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4061,21 +3677,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4085,10 +3701,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599415.1555407417</v>
+        <v>599376</v>
       </c>
       <c r="R32" t="n">
-        <v>7014648.65182882</v>
+        <v>7014558</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4118,19 +3734,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4157,37 +3763,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101620986</v>
+        <v>101620961</v>
       </c>
       <c r="B33" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4197,10 +3798,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599087.9878959882</v>
+        <v>599527</v>
       </c>
       <c r="R33" t="n">
-        <v>7014688.61117007</v>
+        <v>7014614</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4230,19 +3831,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,15 +3860,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101620961</v>
+        <v>101620962</v>
       </c>
       <c r="B34" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4309,10 +3895,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599526.8219983743</v>
+        <v>599344</v>
       </c>
       <c r="R34" t="n">
-        <v>7014614.230910078</v>
+        <v>7014573</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4342,19 +3928,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,15 +3957,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101620985</v>
+        <v>101620963</v>
       </c>
       <c r="B35" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4421,10 +3992,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599347.6687622452</v>
+        <v>599195</v>
       </c>
       <c r="R35" t="n">
-        <v>7014699.766283983</v>
+        <v>7014685</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4454,19 +4025,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4493,15 +4054,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101620948</v>
+        <v>101620969</v>
       </c>
       <c r="B36" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4509,21 +4065,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4533,10 +4089,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599173.6925138293</v>
+        <v>599025</v>
       </c>
       <c r="R36" t="n">
-        <v>7014690.79814464</v>
+        <v>7014654</v>
       </c>
       <c r="S36" t="n">
         <v>50</v>
@@ -4566,19 +4122,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,15 +4151,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>101620990</v>
+        <v>101620978</v>
       </c>
       <c r="B37" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4621,21 +4162,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4645,10 +4186,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599545.1354650052</v>
+        <v>599255</v>
       </c>
       <c r="R37" t="n">
-        <v>7014664.387766092</v>
+        <v>7014645</v>
       </c>
       <c r="S37" t="n">
         <v>50</v>
@@ -4678,19 +4219,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4717,15 +4248,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101620957</v>
+        <v>101620984</v>
       </c>
       <c r="B38" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4733,21 +4259,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4757,10 +4283,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599238.8243959432</v>
+        <v>599233</v>
       </c>
       <c r="R38" t="n">
-        <v>7014701.369776237</v>
+        <v>7014707</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4790,19 +4316,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4829,15 +4345,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101620969</v>
+        <v>101620985</v>
       </c>
       <c r="B39" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4869,10 +4380,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599025.4071435396</v>
+        <v>599348</v>
       </c>
       <c r="R39" t="n">
-        <v>7014653.776860707</v>
+        <v>7014700</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4902,19 +4413,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4941,15 +4442,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101620968</v>
+        <v>101620988</v>
       </c>
       <c r="B40" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4957,39 +4453,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599394.2624401485</v>
+        <v>598993</v>
       </c>
       <c r="R40" t="n">
-        <v>7014667.392392794</v>
+        <v>7014666</v>
       </c>
       <c r="S40" t="n">
         <v>50</v>
@@ -5019,24 +4510,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>trummande</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5063,37 +4539,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101620994</v>
+        <v>101620999</v>
       </c>
       <c r="B41" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5103,10 +4574,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599231.865093591</v>
+        <v>599190</v>
       </c>
       <c r="R41" t="n">
-        <v>7014707.466761513</v>
+        <v>7014701</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5136,19 +4607,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5175,15 +4636,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101620988</v>
+        <v>101621012</v>
       </c>
       <c r="B42" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5215,10 +4671,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>598993.4489214972</v>
+        <v>599262</v>
       </c>
       <c r="R42" t="n">
-        <v>7014665.417396997</v>
+        <v>7014720</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5248,19 +4704,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5287,15 +4733,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>101620991</v>
+        <v>101621013</v>
       </c>
       <c r="B43" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5303,21 +4744,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5327,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599380.5288066471</v>
+        <v>599541</v>
       </c>
       <c r="R43" t="n">
-        <v>7014556.515544325</v>
+        <v>7014653</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5360,19 +4801,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5399,15 +4830,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>101620999</v>
+        <v>101621017</v>
       </c>
       <c r="B44" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5439,10 +4865,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599189.6373784943</v>
+        <v>599213</v>
       </c>
       <c r="R44" t="n">
-        <v>7014700.756263083</v>
+        <v>7014679</v>
       </c>
       <c r="S44" t="n">
         <v>50</v>
@@ -5472,19 +4898,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5511,15 +4927,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>101620955</v>
+        <v>103429197</v>
       </c>
       <c r="B45" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5527,37 +4938,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599185.9322708945</v>
+        <v>599292</v>
       </c>
       <c r="R45" t="n">
-        <v>7014703.797862995</v>
+        <v>7014694</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5581,22 +4992,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5607,53 +5008,57 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>101620952</v>
+        <v>101620986</v>
       </c>
       <c r="B46" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5663,10 +5068,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599262.6997636828</v>
+        <v>599088</v>
       </c>
       <c r="R46" t="n">
-        <v>7014703.007127271</v>
+        <v>7014689</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -5696,19 +5101,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5735,53 +5130,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>101621002</v>
+        <v>103429203</v>
       </c>
       <c r="B47" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>658</v>
+        <v>1205</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599419.6762669433</v>
+        <v>599504</v>
       </c>
       <c r="R47" t="n">
-        <v>7014706.947149363</v>
+        <v>7014630</v>
       </c>
       <c r="S47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5805,22 +5195,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5831,53 +5211,57 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>101620989</v>
+        <v>101620966</v>
       </c>
       <c r="B48" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5887,10 +5271,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>599250.87666217</v>
+        <v>599299</v>
       </c>
       <c r="R48" t="n">
-        <v>7014676.495403576</v>
+        <v>7014696</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -5920,19 +5304,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5959,15 +5333,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>101620963</v>
+        <v>101620993</v>
       </c>
       <c r="B49" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5975,21 +5344,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5999,10 +5368,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599195.0838868237</v>
+        <v>599284</v>
       </c>
       <c r="R49" t="n">
-        <v>7014685.145448151</v>
+        <v>7014654</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6032,19 +5401,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6071,15 +5430,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>101620967</v>
+        <v>101620994</v>
       </c>
       <c r="B50" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6087,21 +5441,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6111,10 +5465,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599330.3819172301</v>
+        <v>599232</v>
       </c>
       <c r="R50" t="n">
-        <v>7014557.673739557</v>
+        <v>7014707</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6144,19 +5498,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6183,15 +5527,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>101620984</v>
+        <v>101621001</v>
       </c>
       <c r="B51" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6199,21 +5538,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6223,10 +5562,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>599232.7670967919</v>
+        <v>599000</v>
       </c>
       <c r="R51" t="n">
-        <v>7014707.494551693</v>
+        <v>7014665</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6256,19 +5595,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6295,53 +5624,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>101620960</v>
+        <v>103429198</v>
       </c>
       <c r="B52" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>599196.6520960084</v>
+        <v>599397</v>
       </c>
       <c r="R52" t="n">
-        <v>7014692.857622771</v>
+        <v>7014616</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6365,22 +5689,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6391,31 +5705,35 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>101620964</v>
+        <v>103429204</v>
       </c>
       <c r="B53" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6423,37 +5741,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>S Torråsberger, Ång</t>
+          <t>Torråsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>599494.3524195094</v>
+        <v>599296</v>
       </c>
       <c r="R53" t="n">
-        <v>7014656.957964102</v>
+        <v>7014691</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6477,22 +5795,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6503,31 +5811,35 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Pekka Bader</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Pekka Bader</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>101620970</v>
+        <v>101620946</v>
       </c>
       <c r="B54" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6535,21 +5847,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6559,10 +5871,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>599375.4841786022</v>
+        <v>599022</v>
       </c>
       <c r="R54" t="n">
-        <v>7014559.064921315</v>
+        <v>7014660</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6592,19 +5904,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6631,15 +5933,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>101620973</v>
+        <v>101620975</v>
       </c>
       <c r="B55" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6647,21 +5944,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6671,10 +5968,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>599390.0823445808</v>
+        <v>599194</v>
       </c>
       <c r="R55" t="n">
-        <v>7014583.409569396</v>
+        <v>7014695</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6704,19 +6001,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6743,15 +6030,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101621013</v>
+        <v>101620997</v>
       </c>
       <c r="B56" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6759,21 +6041,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6783,10 +6065,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>599541.4104560949</v>
+        <v>599523</v>
       </c>
       <c r="R56" t="n">
-        <v>7014653.452870639</v>
+        <v>7014607</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6816,19 +6098,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6855,15 +6127,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>101620978</v>
+        <v>101621018</v>
       </c>
       <c r="B57" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6871,21 +6138,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6895,10 +6162,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>599255.4701371749</v>
+        <v>599415</v>
       </c>
       <c r="R57" t="n">
-        <v>7014644.628674906</v>
+        <v>7014649</v>
       </c>
       <c r="S57" t="n">
         <v>50</v>
@@ -6928,19 +6195,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6967,37 +6224,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>101621012</v>
+        <v>101620960</v>
       </c>
       <c r="B58" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7007,10 +6259,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>599262.6371903267</v>
+        <v>599197</v>
       </c>
       <c r="R58" t="n">
-        <v>7014719.685310815</v>
+        <v>7014693</v>
       </c>
       <c r="S58" t="n">
         <v>50</v>
@@ -7040,19 +6292,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7079,37 +6321,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>101621020</v>
+        <v>101620987</v>
       </c>
       <c r="B59" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7119,10 +6356,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>599527.409587801</v>
+        <v>599025</v>
       </c>
       <c r="R59" t="n">
-        <v>7014639.044617737</v>
+        <v>7014654</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7152,19 +6389,9 @@
           <t>2022-05-25</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2022-05-25</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7191,15 +6418,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>103429200</v>
+        <v>101620992</v>
       </c>
       <c r="B60" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7207,37 +6429,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>599291.8693630168</v>
+        <v>599248</v>
       </c>
       <c r="R60" t="n">
-        <v>7014693.988282376</v>
+        <v>7014661</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7261,22 +6483,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7287,78 +6499,64 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>103429211</v>
+        <v>101620981</v>
       </c>
       <c r="B61" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>599244.0353187171</v>
+        <v>599534</v>
       </c>
       <c r="R61" t="n">
-        <v>7014605.505311808</v>
+        <v>7014678</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7382,22 +6580,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7408,78 +6596,69 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>103429203</v>
+        <v>101620968</v>
       </c>
       <c r="B62" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>599504.6723674607</v>
+        <v>599394</v>
       </c>
       <c r="R62" t="n">
-        <v>7014629.776401671</v>
+        <v>7014668</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7503,22 +6682,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>trummande</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7529,40 +6703,26 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>103429199</v>
+        <v>101620971</v>
       </c>
       <c r="B63" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7570,37 +6730,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>599063.174942647</v>
+        <v>599395</v>
       </c>
       <c r="R63" t="n">
-        <v>7014673.421792979</v>
+        <v>7014657</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7624,22 +6789,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7650,40 +6805,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>103429207</v>
+        <v>101620974</v>
       </c>
       <c r="B64" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7691,37 +6832,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>599057.4902714017</v>
+        <v>599272</v>
       </c>
       <c r="R64" t="n">
-        <v>7014638.083028426</v>
+        <v>7014582</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7745,22 +6891,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7771,40 +6907,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>103429208</v>
+        <v>101620956</v>
       </c>
       <c r="B65" t="n">
-        <v>90052</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7812,37 +6934,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>599490.9355657558</v>
+        <v>599282</v>
       </c>
       <c r="R65" t="n">
-        <v>7014606.810607615</v>
+        <v>7014717</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7866,22 +6988,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7892,78 +7004,64 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>103429201</v>
+        <v>101620965</v>
       </c>
       <c r="B66" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>599260.7852803709</v>
+        <v>599526</v>
       </c>
       <c r="R66" t="n">
-        <v>7014618.644625198</v>
+        <v>7014606</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7987,22 +7085,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8013,78 +7101,64 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>103429210</v>
+        <v>101620972</v>
       </c>
       <c r="B67" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>599501.5987601946</v>
+        <v>599212</v>
       </c>
       <c r="R67" t="n">
-        <v>7014626.976483823</v>
+        <v>7014701</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8108,22 +7182,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8134,40 +7198,26 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>103429204</v>
+        <v>101620989</v>
       </c>
       <c r="B68" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8175,37 +7225,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>599296.0117051159</v>
+        <v>599251</v>
       </c>
       <c r="R68" t="n">
-        <v>7014691.41108355</v>
+        <v>7014677</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8229,22 +7279,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8255,78 +7295,64 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>103429197</v>
+        <v>101621007</v>
       </c>
       <c r="B69" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>599291.8693630168</v>
+        <v>599504</v>
       </c>
       <c r="R69" t="n">
-        <v>7014693.988282376</v>
+        <v>7014697</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8350,22 +7376,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8376,40 +7392,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>103429198</v>
+        <v>101621016</v>
       </c>
       <c r="B70" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8417,37 +7419,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>599396.7350365533</v>
+        <v>599197</v>
       </c>
       <c r="R70" t="n">
-        <v>7014616.525494043</v>
+        <v>7014688</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8471,22 +7473,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8497,78 +7489,64 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>103429205</v>
+        <v>101621020</v>
       </c>
       <c r="B71" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>599277.9031538509</v>
+        <v>599527</v>
       </c>
       <c r="R71" t="n">
-        <v>7014605.196533603</v>
+        <v>7014639</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8592,22 +7570,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8618,78 +7586,64 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>103429209</v>
+        <v>101620977</v>
       </c>
       <c r="B72" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Torråsbäcken, Ång</t>
+          <t>S Torråsberger, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>599400.4327779964</v>
+        <v>599271</v>
       </c>
       <c r="R72" t="n">
-        <v>7014628.361122312</v>
+        <v>7014696</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8713,22 +7667,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8739,28 +7683,19 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Pekka Bader</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17415-2022 artfynd.xlsx
+++ b/artfynd/A 17415-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AZ72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620948</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620951</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620955</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620967</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620970</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620973</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620980</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620990</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620991</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620996</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621002</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621006</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621009</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621015</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621019</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2427,6 +2517,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429199</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429200</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2639,6 +2739,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429201</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2745,6 +2850,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429205</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2851,6 +2961,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429207</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2957,6 +3072,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429209</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3063,6 +3183,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429210</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3169,6 +3294,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429211</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3275,6 +3405,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429208</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3372,6 +3507,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620964</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3469,6 +3609,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620949</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3566,6 +3711,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620952</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3663,6 +3813,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620953</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3760,6 +3915,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620954</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3857,6 +4017,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620961</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3954,6 +4119,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620962</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4051,6 +4221,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620963</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4148,6 +4323,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620969</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4245,6 +4425,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620978</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4342,6 +4527,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620984</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4439,6 +4629,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620985</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4536,6 +4731,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620988</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4633,6 +4833,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620999</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4730,6 +4935,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621012</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4827,6 +5037,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621013</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4924,6 +5139,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621017</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5030,6 +5250,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429197</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5127,6 +5352,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620986</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5233,6 +5463,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429203</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5330,6 +5565,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620966</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5427,6 +5667,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620993</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5524,6 +5769,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620994</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5621,6 +5871,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621001</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5727,6 +5982,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429198</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5833,6 +6093,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103429204</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5930,6 +6195,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620946</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6027,6 +6297,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620975</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6124,6 +6399,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620997</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6221,6 +6501,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621018</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6318,6 +6603,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620960</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6415,6 +6705,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620987</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6512,6 +6807,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620992</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6609,6 +6909,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620981</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6716,6 +7021,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620968</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6818,6 +7128,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620971</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6920,6 +7235,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620974</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7017,6 +7337,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620956</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7114,6 +7439,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620965</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7211,6 +7541,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620972</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7308,6 +7643,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620989</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7405,6 +7745,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621007</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7502,6 +7847,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621016</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7599,6 +7949,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101621020</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7696,8 +8051,86 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101620977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>